--- a/report_G5.xlsx
+++ b/report_G5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c67c286bfbc60b87/Documents/VScode/agile_scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC1EF03-6B01-4263-AEF0-79DE3B5C1CF3}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBFA0289-9D20-4389-9B6C-CAA236A4D754}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1075,17 +1075,17 @@
       <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>10</v>
+      <c r="C8" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="D8" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" s="6">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>11</v>
@@ -1110,16 +1110,16 @@
         <v>24</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>11</v>
@@ -1144,13 +1144,13 @@
         <v>30</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>9</v>
@@ -1178,16 +1178,16 @@
         <v>32</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E11" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>11</v>
@@ -1212,16 +1212,16 @@
         <v>33</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>11</v>
@@ -1247,10 +1247,7 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8 F8" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>$M$8:$M$11</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$N$8:$N$11</formula1>
     </dataValidation>

--- a/report_G5.xlsx
+++ b/report_G5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c67c286bfbc60b87/Documents/VScode/agile_scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBFA0289-9D20-4389-9B6C-CAA236A4D754}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{018F3A80-0F95-443D-A184-54D243D1D451}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
   <si>
     <t>STT</t>
   </si>
@@ -144,6 +144,18 @@
   </si>
   <si>
     <t>Link Video:</t>
+  </si>
+  <si>
+    <t>Bài 10 chưa rõ yêu cầu hệ thống cần làm ("ứng dụng quản lý công việc bạn đã tạo ở bài tập 2" nhưng bài 2 là quản lý thanh toán)</t>
+  </si>
+  <si>
+    <t>https://github.com/quangduymanh/QuangDuyManh_PTIT-HN-131_IT106_Session-02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=r8UdtbiI3bI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yQzDR3V7ig0</t>
   </si>
 </sst>
 </file>
@@ -298,7 +310,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -365,6 +377,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -928,6 +946,9 @@
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="C14" s="24" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -953,6 +974,7 @@
     <hyperlink ref="J10" r:id="rId3" xr:uid="{2BB8FCA9-B6BB-4C1E-A303-FCEB71DA47F1}"/>
     <hyperlink ref="J11" r:id="rId4" xr:uid="{A77FC0A2-C9E3-4E94-92C0-32C72A1DBCDA}"/>
     <hyperlink ref="J12" r:id="rId5" xr:uid="{15C72327-65A2-4FC8-BACB-3A8CEDA524DF}"/>
+    <hyperlink ref="C14" r:id="rId6" xr:uid="{24C06A82-0D64-44DF-829B-7276F7E5EBC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1090,8 +1112,10 @@
       <c r="G8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="8"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="J8" s="15" t="s">
         <v>25</v>
       </c>
@@ -1229,12 +1253,15 @@
       <c r="H12" s="16"/>
       <c r="I12" s="6"/>
       <c r="J12" s="15" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1258,6 +1285,7 @@
     <hyperlink ref="J10" r:id="rId3" xr:uid="{19D6CB94-5346-4E94-897D-280E62AAF32F}"/>
     <hyperlink ref="J11" r:id="rId4" xr:uid="{F70C241D-622B-4C36-822B-2CBDB09513DD}"/>
     <hyperlink ref="J12" r:id="rId5" xr:uid="{10B0FCF5-C8A2-45C5-BE88-168A94FCDF08}"/>
+    <hyperlink ref="C14" r:id="rId6" xr:uid="{FBE688CF-B5D4-4375-9F88-F563E5227B46}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/report_G5.xlsx
+++ b/report_G5.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c67c286bfbc60b87/Documents/VScode/agile_scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{018F3A80-0F95-443D-A184-54D243D1D451}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79356432-21DA-47B5-8223-CF556183A406}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ss1" sheetId="2" r:id="rId1"/>
     <sheet name="ss2" sheetId="1" r:id="rId2"/>
+    <sheet name="ss3" sheetId="3" r:id="rId3"/>
+    <sheet name="ss4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="57">
   <si>
     <t>STT</t>
   </si>
@@ -156,6 +158,42 @@
   </si>
   <si>
     <t>https://youtu.be/yQzDR3V7ig0</t>
+  </si>
+  <si>
+    <t>Session: 3</t>
+  </si>
+  <si>
+    <t>Ngày báo cáo: 24/11/2025</t>
+  </si>
+  <si>
+    <t>https://github.com/quangduymanh/QuangDuyManh_PTIT-HN-131_IT106_Session-03</t>
+  </si>
+  <si>
+    <t>Bài 8 thiếu lập kế hoạch</t>
+  </si>
+  <si>
+    <t>Bài làm ổn nhưng ước lượng Story Point chưa chuẩn xác</t>
+  </si>
+  <si>
+    <t>Bài làm đầy đủ, chi tiết, rõ ràng</t>
+  </si>
+  <si>
+    <t>Bài làm cơ bản đầy đủ, Planning pocket thiếu quá trình tổng hợp điểm và đưa ra lý do</t>
+  </si>
+  <si>
+    <t>Quên bật mic ghi âm trong quá trình báo cáo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UL7qX8IY81g</t>
+  </si>
+  <si>
+    <t>Session: 4</t>
+  </si>
+  <si>
+    <t>Ngày báo cáo: 25/11/2025</t>
+  </si>
+  <si>
+    <t>https://github.com/quangduymanh/QuangDuyManh_PTIT-HN-131_IT106_Session-04</t>
   </si>
 </sst>
 </file>
@@ -310,7 +348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -363,6 +401,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -377,12 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -680,54 +724,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.65" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="3" spans="1:14" ht="20.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21" t="s">
+      <c r="F3" s="25"/>
+      <c r="G3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="21"/>
+      <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:14" ht="20.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -946,7 +990,7 @@
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="19" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1002,54 +1046,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.65" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="3" spans="1:14" ht="20.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="22" t="s">
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21" t="s">
+      <c r="F3" s="25"/>
+      <c r="G3" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="21"/>
+      <c r="H3" s="25"/>
     </row>
     <row r="4" spans="1:14" ht="20.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1112,8 +1156,8 @@
       <c r="G8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23" t="s">
+      <c r="H8" s="18"/>
+      <c r="I8" s="18" t="s">
         <v>41</v>
       </c>
       <c r="J8" s="15" t="s">
@@ -1260,7 +1304,7 @@
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1289,4 +1333,631 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA249543-AEDB-4010-8FD9-509FFEA48FB1}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.7109375" style="1"/>
+    <col min="13" max="13" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="38.65" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.25">
+      <c r="A3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="25"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.25">
+      <c r="A4" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.25">
+      <c r="A5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" ht="33">
+      <c r="A7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="33">
+      <c r="A8" s="6">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6">
+        <v>8</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="J8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6">
+        <v>8</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="49.5">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6">
+        <v>9</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>8</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="6"/>
+      <c r="J11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="33">
+      <c r="A12" s="6">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="6">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6">
+        <v>8</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="6"/>
+      <c r="J12" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="H16" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G12" xr:uid="{C8D9B2D5-AB36-42D0-8EC6-3F82820E6F86}">
+      <formula1>$N$8:$N$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J8" r:id="rId1" xr:uid="{E1F33704-E011-4793-B093-16E86829012D}"/>
+    <hyperlink ref="J9" r:id="rId2" xr:uid="{B6D2CD3C-483A-498C-912B-FDA2BAA9CEE6}"/>
+    <hyperlink ref="J10" r:id="rId3" xr:uid="{0B738E76-78A1-4B6D-9CE3-9F69C3C05402}"/>
+    <hyperlink ref="J11" r:id="rId4" xr:uid="{3E0C58EF-A64A-4B81-B8EE-9BBA0072861B}"/>
+    <hyperlink ref="J12" r:id="rId5" xr:uid="{91F28BC0-0DED-4672-BF0D-AB59D010B307}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1002DBA8-5267-4577-9C5F-8027A75A120A}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.7109375" style="1"/>
+    <col min="13" max="13" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="38.65" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.25">
+      <c r="A3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="25"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.25">
+      <c r="A4" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.25">
+      <c r="A5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" ht="33">
+      <c r="A7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6">
+        <v>10</v>
+      </c>
+      <c r="E8" s="6">
+        <v>10</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6">
+        <v>10</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="6">
+        <v>10</v>
+      </c>
+      <c r="E10" s="6">
+        <v>10</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6">
+        <v>10</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6">
+        <v>10</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G12" xr:uid="{9BAD787A-AB17-4480-995A-36E27C17ABF3}">
+      <formula1>$N$8:$N$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J8" r:id="rId1" xr:uid="{EA8CD2F9-DEC7-4B36-AE42-7BAE97CCBCCB}"/>
+    <hyperlink ref="J9" r:id="rId2" xr:uid="{5497B575-CA71-4795-AB64-97E30052560C}"/>
+    <hyperlink ref="J10" r:id="rId3" xr:uid="{0F373711-5E5A-4B5C-B60D-3187A05EC981}"/>
+    <hyperlink ref="J11" r:id="rId4" xr:uid="{0132369F-A3E5-4C51-961E-BCB9022BE089}"/>
+    <hyperlink ref="J12" r:id="rId5" xr:uid="{42607A71-4252-4E55-B471-DCD53A72E2E1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/report_G5.xlsx
+++ b/report_G5.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c67c286bfbc60b87/Documents/VScode/agile_scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79356432-21DA-47B5-8223-CF556183A406}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{E16B03F4-24E3-4F7A-AF81-CCC404D8F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C34942B4-150B-4852-8CD1-7779FCA70A1F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ss1" sheetId="2" r:id="rId1"/>
     <sheet name="ss2" sheetId="1" r:id="rId2"/>
     <sheet name="ss3" sheetId="3" r:id="rId3"/>
     <sheet name="ss4" sheetId="4" r:id="rId4"/>
+    <sheet name="ss5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="64">
   <si>
     <t>STT</t>
   </si>
@@ -194,6 +195,27 @@
   </si>
   <si>
     <t>https://github.com/quangduymanh/QuangDuyManh_PTIT-HN-131_IT106_Session-04</t>
+  </si>
+  <si>
+    <t>Burndown chart chưa vẽ rõ đường lý tưởng và đường thực tế</t>
+  </si>
+  <si>
+    <t>Bài làm đầy đủ, chi tiết</t>
+  </si>
+  <si>
+    <t>Thiếu một số biểu đồ</t>
+  </si>
+  <si>
+    <t>Burndown chart thiếu đường lý tưởng</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ddwlcp2JcIQ</t>
+  </si>
+  <si>
+    <t>Session: 5</t>
+  </si>
+  <si>
+    <t>Ngày báo cáo: 27/11/2025</t>
   </si>
 </sst>
 </file>
@@ -1774,21 +1796,23 @@
         <v>22</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E8" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="18"/>
+      <c r="H8" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="I8" s="18"/>
       <c r="J8" s="15" t="s">
         <v>25</v>
@@ -1800,7 +1824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" ht="33">
       <c r="A9" s="6">
         <v>2</v>
       </c>
@@ -1808,21 +1832,23 @@
         <v>24</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="16"/>
+      <c r="H9" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="I9" s="6"/>
       <c r="J9" s="15" t="s">
         <v>26</v>
@@ -1842,21 +1868,23 @@
         <v>30</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E10" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="16"/>
+      <c r="H10" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="I10" s="6"/>
       <c r="J10" s="15" t="s">
         <v>27</v>
@@ -1876,21 +1904,23 @@
         <v>32</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="16"/>
+      <c r="H11" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="I11" s="6"/>
       <c r="J11" s="15" t="s">
         <v>28</v>
@@ -1910,21 +1940,23 @@
         <v>33</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E12" s="6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="I12" s="6"/>
       <c r="J12" s="15" t="s">
         <v>56</v>
@@ -1934,7 +1966,9 @@
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1960,4 +1994,310 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{477292E9-6119-4BB0-BAC9-2767889EE909}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="7.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.7109375" style="1"/>
+    <col min="13" max="13" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="38.65" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="3" spans="1:14" ht="20.25">
+      <c r="A3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="25"/>
+    </row>
+    <row r="4" spans="1:14" ht="20.25">
+      <c r="A4" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.25">
+      <c r="A5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="20.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" ht="33">
+      <c r="A7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6">
+        <v>6</v>
+      </c>
+      <c r="E8" s="6">
+        <v>6</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="6">
+        <v>6</v>
+      </c>
+      <c r="E9" s="6">
+        <v>6</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="6">
+        <v>6</v>
+      </c>
+      <c r="E10" s="6">
+        <v>6</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6">
+        <v>6</v>
+      </c>
+      <c r="E11" s="6">
+        <v>6</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="16"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6">
+        <v>6</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G8:G12" xr:uid="{955C7010-85A4-45AC-BBD4-F73D38ABC309}">
+      <formula1>$N$8:$N$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="J8" r:id="rId1" xr:uid="{702AAC03-78B2-4BCB-94E2-D6B4359A6DBA}"/>
+    <hyperlink ref="J9" r:id="rId2" xr:uid="{93BF62CD-16E4-410F-92BA-7BE630139238}"/>
+    <hyperlink ref="J10" r:id="rId3" xr:uid="{A7EF3F70-2B72-4165-A38C-2C0422D829DC}"/>
+    <hyperlink ref="J11" r:id="rId4" xr:uid="{91AB8A2F-4C33-4F7E-BB6F-B1CFBADF4419}"/>
+    <hyperlink ref="J12" r:id="rId5" xr:uid="{7452D199-A798-408C-B6AD-44F058DFE8A0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>